--- a/01-ISMS-Scope/Interested-Parties.xlsx
+++ b/01-ISMS-Scope/Interested-Parties.xlsx
@@ -29,7 +29,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="58">
   <si>
-    <t xml:space="preserve">Simulated portfolio project - SecurePay Technologies Pvt. Ltd. is fictional. Not a certification claim. (ISO 27001 clause 4.1)</t>
+    <t xml:space="preserve">Simulated portfolio project - HawkPay Technologies Pvt. Ltd. is fictional. Not a certification claim. (ISO 27001 clause 4.1)</t>
   </si>
   <si>
     <t xml:space="preserve">Type</t>
